--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111317</v>
+        <v>111324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111324</v>
+        <v>111325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111325</v>
+        <v>111330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111330</v>
+        <v>111332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22780-2026 artfynd.xlsx
+++ b/artfynd/A 22780-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136419374</v>
       </c>
       <c r="B2" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
